--- a/docs/Kエナジー_DD/KE特高系統用蓄電池リスト_20260929_弊社確認追記.xlsx
+++ b/docs/Kエナジー_DD/KE特高系統用蓄電池リスト_20260929_弊社確認追記.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$B$1:$R$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$B$1:$N$18</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -266,64 +266,64 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="56" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:R18"/>
+  <dimension ref="B1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="2.85546875" customWidth="1" style="27" min="1" max="1"/>
@@ -746,14 +746,10 @@
     <col width="26.85546875" customWidth="1" style="29" min="8" max="8"/>
     <col width="22.140625" customWidth="1" style="27" min="9" max="9"/>
     <col width="10" customWidth="1" style="27" min="10" max="10"/>
-    <col width="24" customWidth="1" style="38" min="11" max="11"/>
-    <col width="30" customWidth="1" style="38" min="12" max="12"/>
-    <col width="28" customWidth="1" style="38" min="13" max="13"/>
-    <col width="18" customWidth="1" style="38" min="14" max="14"/>
-    <col width="30" customWidth="1" style="38" min="15" max="15"/>
-    <col width="32" customWidth="1" style="38" min="16" max="16"/>
-    <col width="46" customWidth="1" style="38" min="17" max="17"/>
-    <col width="60" customWidth="1" style="38" min="18" max="18"/>
+    <col width="22" customWidth="1" style="38" min="11" max="11"/>
+    <col width="44" customWidth="1" style="38" min="12" max="12"/>
+    <col width="44" customWidth="1" style="38" min="13" max="13"/>
+    <col width="40" customWidth="1" style="38" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="38" thickBot="1">
@@ -823,41 +819,21 @@
       </c>
       <c r="L2" s="37" t="inlineStr">
         <is>
-          <t>災害ハザード</t>
+          <t>DD結果（○問題なし／△要確認／×課題あり）</t>
         </is>
       </c>
       <c r="M2" s="37" t="inlineStr">
         <is>
-          <t>都市計画・自然公園</t>
+          <t>主な留意点</t>
         </is>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
-          <t>地形（半径100m内の高低差）</t>
-        </is>
-      </c>
-      <c r="O2" s="37" t="inlineStr">
-        <is>
-          <t>道路・搬入</t>
-        </is>
-      </c>
-      <c r="P2" s="37" t="inlineStr">
-        <is>
-          <t>最寄り変電所</t>
-        </is>
-      </c>
-      <c r="Q2" s="37" t="inlineStr">
-        <is>
-          <t>弊社所見</t>
-        </is>
-      </c>
-      <c r="R2" s="37" t="inlineStr">
-        <is>
           <t>ご確認のお願い</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="96" customFormat="1" customHeight="1" s="29">
+    <row r="3" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B3" s="41" t="n">
         <v>1</v>
       </c>
@@ -900,43 +876,22 @@
       </c>
       <c r="L3" s="48" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし</t>
+          <t>ハザード○　法規制○　地形○　搬入△　系統△</t>
         </is>
       </c>
       <c r="M3" s="48" t="inlineStr">
         <is>
-          <t>都市計画区域（区域区分なし）・用途地域なし</t>
+          <t>154kV線に近接・平坦。敷地0.49haで規模は小さめ</t>
         </is>
       </c>
       <c r="N3" s="48" t="inlineStr">
         <is>
-          <t>約10m（標高 約544m）</t>
-        </is>
-      </c>
-      <c r="O3" s="48" t="inlineStr">
-        <is>
-          <t>最寄道路 約36m（幅3m未満）／幅5.5m以上まで約744m</t>
-        </is>
-      </c>
-      <c r="P3" s="48" t="inlineStr">
-        <is>
-          <t>更科変電所（66kV）約2.0km／会津変電所（154kV）約10.8km</t>
-        </is>
-      </c>
-      <c r="Q3" s="48" t="inlineStr">
-        <is>
-          <t>154kV送電線に近接し、地形も平坦。上位変電所にも比較的余裕あり。敷地面積が小さく規模は限定的</t>
-        </is>
-      </c>
-      <c r="R3" s="48" t="inlineStr">
-        <is>
-          <t>①座標の地点が大字更科側に位置しているため、地番（磐根4100-29）との位置照合をお願いします
-②隣接地を含めた拡張の可否
-③垂直積雪量の把握状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="96" customFormat="1" customHeight="1" s="29">
+          <t>①座標と地番の位置照合（座標は大字更科側）
+②隣接地を含めた拡張可否</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B4" s="49" t="n">
         <v>1</v>
       </c>
@@ -977,43 +932,22 @@
       </c>
       <c r="L4" s="51" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし</t>
+          <t>ハザード○　法規制△　地形×　搬入×　系統×</t>
         </is>
       </c>
       <c r="M4" s="51" t="inlineStr">
         <is>
-          <t>都市計画区域外（花園花貫県立自然公園の境界まで約135m）</t>
+          <t>275kV線に近接。敷地0.2haは特高設備に狭く、搬入路も遠い</t>
         </is>
       </c>
       <c r="N4" s="51" t="inlineStr">
         <is>
-          <t>約45m（標高 約432m）</t>
-        </is>
-      </c>
-      <c r="O4" s="51" t="inlineStr">
-        <is>
-          <t>最寄道路 約285m（幅3m未満）／幅5.5m以上は1.5km圏内になし</t>
-        </is>
-      </c>
-      <c r="P4" s="51" t="inlineStr">
-        <is>
-          <t>木皿変電所（66kV）約3.5km／常磐変電所（275kV）約12.0km</t>
-        </is>
-      </c>
-      <c r="Q4" s="51" t="inlineStr">
-        <is>
-          <t>275kV送電線に近接するが、敷地約0.2haは特高設備の設置には狭い。周辺系統の空容量も厳しい</t>
-        </is>
-      </c>
-      <c r="R4" s="51" t="inlineStr">
-        <is>
-          <t>①座標の地点が磯原町大塚側に位置しているため、地番（木皿703）との位置照合をお願いします
-②隣接地を含めた拡張の可否
-③現地までの進入路（幅員）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="96" customFormat="1" customHeight="1" s="29">
+          <t>①座標と地番の位置照合（座標は磯原町大塚側）
+②隣接地を含めた拡張可否</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B5" s="49" t="n">
         <v>1</v>
       </c>
@@ -1056,42 +990,22 @@
       </c>
       <c r="L5" s="51" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし（土砂災害警戒区域まで約390m）</t>
+          <t>ハザード○　法規制×　地形×　搬入△　系統×</t>
         </is>
       </c>
       <c r="M5" s="51" t="inlineStr">
         <is>
-          <t>市街化調整区域</t>
+          <t>66kV線が敷地上空を通過。市街化調整区域</t>
         </is>
       </c>
       <c r="N5" s="51" t="inlineStr">
         <is>
-          <t>約46m（標高 約456m）</t>
-        </is>
-      </c>
-      <c r="O5" s="51" t="inlineStr">
-        <is>
-          <t>最寄道路 約121m（幅3m未満）／幅5.5m以上まで約577m</t>
-        </is>
-      </c>
-      <c r="P5" s="51" t="inlineStr">
-        <is>
-          <t>田方変電所（154kV）約4.6km</t>
-        </is>
-      </c>
-      <c r="Q5" s="51" t="inlineStr">
-        <is>
-          <t>66kV送電線が敷地上空を通過。市街化調整区域のため開発許可の要否確認が必要。周辺系統の空容量は厳しい</t>
-        </is>
-      </c>
-      <c r="R5" s="51" t="inlineStr">
-        <is>
-          <t>①市街化調整区域での開発許可について、市への相談状況
-②送電線の線下となる範囲（離隔・地役権）の扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="96" customFormat="1" customHeight="1" s="29">
+          <t>①開発許可に関する市への相談状況
+②送電線下の範囲の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B6" s="49" t="n">
         <v>1</v>
       </c>
@@ -1134,42 +1048,22 @@
       </c>
       <c r="L6" s="58" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし</t>
+          <t>ハザード○　法規制○　地形△　搬入△　系統×</t>
         </is>
       </c>
       <c r="M6" s="58" t="inlineStr">
         <is>
-          <t>都市計画区域（区域区分なし）・用途地域なし</t>
+          <t>154kV線に近接。上位系統の混雑で増強の可能性</t>
         </is>
       </c>
       <c r="N6" s="58" t="inlineStr">
         <is>
-          <t>約36m（標高 約172m）</t>
-        </is>
-      </c>
-      <c r="O6" s="58" t="inlineStr">
-        <is>
-          <t>最寄道路 約20m（幅3m未満）／幅5.5m以上まで約758m</t>
-        </is>
-      </c>
-      <c r="P6" s="58" t="inlineStr">
-        <is>
-          <t>東山変電所（66kV）約1.9km／水沢変電所（275kV）約10.0km</t>
-        </is>
-      </c>
-      <c r="Q6" s="58" t="inlineStr">
-        <is>
-          <t>154kV送電線に近接。上位系統（一関・水沢方面）の混雑により増強工事の可能性あり</t>
-        </is>
-      </c>
-      <c r="R6" s="58" t="inlineStr">
-        <is>
-          <t>①現地までの進入路（幅員・舗装）
-②森林法（林地開発許可）の確認状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="96" customFormat="1" customHeight="1" s="29">
+          <t>①進入路の状況
+②林地開発許可の確認状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B7" s="49" t="n">
         <v>1</v>
       </c>
@@ -1212,42 +1106,22 @@
       </c>
       <c r="L7" s="51" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし（土砂災害警戒区域まで約200m、大規模盛土造成地まで約100m）</t>
+          <t>ハザード△　法規制○　地形△　搬入○　系統△</t>
         </is>
       </c>
       <c r="M7" s="51" t="inlineStr">
         <is>
-          <t>都市計画区域外・用途地域なし</t>
+          <t>154kV線に近接・道路良好。上位系統の混雑で増強の可能性</t>
         </is>
       </c>
       <c r="N7" s="51" t="inlineStr">
         <is>
-          <t>約30m（標高 約139m）</t>
-        </is>
-      </c>
-      <c r="O7" s="51" t="inlineStr">
-        <is>
-          <t>最寄道路 約31m（幅3m未満）／幅5.5m以上まで約39m</t>
-        </is>
-      </c>
-      <c r="P7" s="51" t="inlineStr">
-        <is>
-          <t>千厩変電所（66kV）約3.8km／気仙沼変電所（154kV）約17.1km</t>
-        </is>
-      </c>
-      <c r="Q7" s="51" t="inlineStr">
-        <is>
-          <t>154kV送電線に近接し、道路条件も良好。上位系統（一関・水沢方面）の混雑により増強工事の可能性あり</t>
-        </is>
-      </c>
-      <c r="R7" s="51" t="inlineStr">
-        <is>
-          <t>①隣接する盛土造成地・警戒区域との位置関係
-②現地までの進入路の状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="96" customFormat="1" customHeight="1" s="29">
+          <t>①隣接する盛土造成地との位置関係
+②進入路の状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B8" s="49" t="n">
         <v>1</v>
       </c>
@@ -1290,43 +1164,22 @@
       </c>
       <c r="L8" s="51" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし</t>
+          <t>ハザード○　法規制○　地形△　搬入△　系統×</t>
         </is>
       </c>
       <c r="M8" s="51" t="inlineStr">
         <is>
-          <t>都市計画区域（区域区分なし）・用途地域なし</t>
+          <t>66kV線に近接・敷地広い。上位154kV系統は増強予定</t>
         </is>
       </c>
       <c r="N8" s="51" t="inlineStr">
         <is>
-          <t>約29m（標高 約109m）</t>
-        </is>
-      </c>
-      <c r="O8" s="51" t="inlineStr">
-        <is>
-          <t>最寄道路 約20m（幅3m未満）／幅5.5m以上まで約730m</t>
-        </is>
-      </c>
-      <c r="P8" s="51" t="inlineStr">
-        <is>
-          <t>中村変電所（66kV）約4.6km／駒ヶ嶺変電所（154kV）約10.1km</t>
-        </is>
-      </c>
-      <c r="Q8" s="51" t="inlineStr">
-        <is>
-          <t>66kV送電線に近接し敷地は広い。上位の154kV系統は増強工事予定があり、連系時期・規模に影響の可能性</t>
-        </is>
-      </c>
-      <c r="R8" s="51" t="inlineStr">
-        <is>
-          <t>①地積のうち利用予定の範囲
-②森林法（林地開発許可）の確認状況
-③現地までの進入路（幅員）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="96" customFormat="1" customHeight="1" s="29">
+          <t>①利用予定の範囲
+②林地開発許可の確認状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customFormat="1" customHeight="1" s="29">
       <c r="B9" s="49" t="n">
         <v>1</v>
       </c>
@@ -1373,39 +1226,18 @@
       </c>
       <c r="L9" s="51" t="inlineStr">
         <is>
-          <t>浸水・土砂・液状化：該当なし</t>
+          <t>ハザード○　法規制○　地形△　搬入×　系統△</t>
         </is>
       </c>
       <c r="M9" s="51" t="inlineStr">
         <is>
-          <t>都市計画区域（区域区分なし）・用途地域なし</t>
+          <t>近傍に送電線なし（約4.4km）。接道なし</t>
         </is>
       </c>
       <c r="N9" s="51" t="inlineStr">
         <is>
-          <t>約27m（標高 約99m）</t>
-        </is>
-      </c>
-      <c r="O9" s="51" t="inlineStr">
-        <is>
-          <t>最寄道路 約327m（幅3m未満）／幅5.5m以上まで約557m</t>
-        </is>
-      </c>
-      <c r="P9" s="51" t="inlineStr">
-        <is>
-          <t>加治木変電所（66kV）約4.9km／霧島変電所（220kV）約15.7km</t>
-        </is>
-      </c>
-      <c r="Q9" s="51" t="inlineStr">
-        <is>
-          <t>近傍に送電線がなく、連系には長距離の自営線が必要となる見込み。接道なし</t>
-        </is>
-      </c>
-      <c r="R9" s="51" t="inlineStr">
-        <is>
-          <t>①連系方法の想定（最寄り送電線まで約4.4km）
-②接道状況・進入路の確保方法
-③地積のうち利用予定の範囲</t>
+          <t>①連系方法の想定
+②進入路の確保方法</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1259,7 @@
     <row r="14">
       <c r="B14" s="64" t="inlineStr">
         <is>
-          <t>【J列以降について】弊社による机上確認の結果です（現地確認前）。</t>
+          <t>【J列以降について】弊社による机上確認の結果です（現地確認前）。DD結果の区分：ハザード＝浸水・土砂・液状化、法規制＝都市計画・自然公園等、地形＝周辺の高低差、搬入＝道路幅員・距離、系統＝周辺変電所の空容量・混雑。</t>
         </is>
       </c>
     </row>
